--- a/public/data/upcoming-events.xlsx
+++ b/public/data/upcoming-events.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>Event name</t>
   </si>
@@ -34,30 +34,23 @@
     <t>Registration Link</t>
   </si>
   <si>
-    <t/>
+    <t>Genesis</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="h:mm tt"/>
-    <numFmt numFmtId="165" formatCode="h:mm Am/Pm"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="h:mm Am/Pm"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -93,27 +86,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="165" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="165" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -421,15 +408,15 @@
   <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="6" width="19.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="6" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="7" width="11.005" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="6" width="20.14785714285714" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="6" width="19.433571428571426" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="6" width="23.290714285714284" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="4" width="19.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="4" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="5" width="11.005" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="4" width="20.14785714285714" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="4" width="19.433571428571426" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="4" width="23.290714285714284" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -450,166 +437,78 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="5"/>
-      <c r="D3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="B2" s="1"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
-      <c r="A4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
-      <c r="A5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="5"/>
-      <c r="D5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
-      <c r="A6" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
-      <c r="A7" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="5"/>
-      <c r="D7" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
-      <c r="A8" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
-      <c r="A9" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" s="5"/>
-      <c r="D9" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
-      <c r="A10" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C10" s="4"/>
-      <c r="D10" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/public/data/upcoming-events.xlsx
+++ b/public/data/upcoming-events.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="7">
   <si>
     <t>Event name</t>
   </si>
@@ -443,7 +443,9 @@
       <c r="B2" s="1"/>
       <c r="C2" s="3"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
+      <c r="E2" s="1" t="s">
+        <v>6</v>
+      </c>
       <c r="F2" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
